--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E9F075-D840-4165-83BD-5B2D9F38AE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95AFFB3-F6DA-4E55-B9D0-B7FD5BCEA313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="120">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -4093,9 +4093,11 @@
       <c r="K7" s="33"/>
       <c r="L7" s="34"/>
       <c r="M7" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="N7" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="N7" s="33"/>
       <c r="O7" s="33"/>
       <c r="P7" s="33"/>
       <c r="Q7" s="33"/>
@@ -4730,11 +4732,11 @@
       </c>
       <c r="M17" s="41">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="41">
+        <f t="shared" si="2"/>
         <v>1</v>
-      </c>
-      <c r="N17" s="41">
-        <f t="shared" si="2"/>
-        <v>0</v>
       </c>
       <c r="O17" s="41">
         <f t="shared" si="2"/>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95AFFB3-F6DA-4E55-B9D0-B7FD5BCEA313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60331D28-03CF-4FA6-A413-116692F874EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="120">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L5" s="5">
         <f>IF(ISNUMBER(سبتمبر!AK7),سبتمبر!AK7,"")</f>
-        <v>6300000</v>
+        <v>6066666.6699999999</v>
       </c>
       <c r="M5" s="5">
         <f>IF(ISNUMBER(أكتوبر!AL7),أكتوبر!AL7,"")</f>
@@ -1442,11 +1442,11 @@
       </c>
       <c r="P5" s="6">
         <f>IF(ISNUMBER(يناير!AK7),يناير!AK7,0)+IF(ISNUMBER(فبراير!AH7),فبراير!AH7,0)+IF(ISNUMBER(مارس!AK7),مارس!AK7,0)+IF(ISNUMBER(أبريل!AJ7),أبريل!AJ7,0)+IF(ISNUMBER(مايو!AK7),مايو!AK7,0)+IF(ISNUMBER(يونيو!AJ7),يونيو!AJ7,0)+IF(ISNUMBER(يوليو!AK7),يوليو!AK7,0)+IF(ISNUMBER(أغسطس!AK7),أغسطس!AK7,0)+IF(ISNUMBER(سبتمبر!AJ7),سبتمبر!AJ7,0)+IF(ISNUMBER(أكتوبر!AK7),أكتوبر!AK7,0)+IF(ISNUMBER(نوفمبر!AJ7),نوفمبر!AJ7,0)+IF(ISNUMBER(ديسمبر!AK7),ديسمبر!AK7,0)</f>
-        <v>4787096.78</v>
+        <v>5020430.1100000003</v>
       </c>
       <c r="Q5" s="7">
         <f t="shared" ref="Q5:Q14" si="0">IFERROR(SUM(D5:O5),"")</f>
-        <v>80846236.530000001</v>
+        <v>80612903.200000003</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="L15" s="11">
         <f t="shared" si="1"/>
-        <v>14600000</v>
+        <v>14366666.67</v>
       </c>
       <c r="M15" s="11">
         <f t="shared" si="1"/>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="P15" s="12">
         <f t="shared" si="1"/>
-        <v>10366236.58</v>
+        <v>10599569.91</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>176311861.53999999</v>
+        <v>176078528.20999998</v>
       </c>
     </row>
   </sheetData>
@@ -4104,7 +4104,9 @@
       <c r="R7" s="33"/>
       <c r="S7" s="34"/>
       <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
+      <c r="U7" s="33" t="s">
+        <v>39</v>
+      </c>
       <c r="V7" s="33"/>
       <c r="W7" s="33"/>
       <c r="X7" s="33"/>
@@ -4117,7 +4119,7 @@
       <c r="AE7" s="33"/>
       <c r="AF7" s="35">
         <f t="shared" ref="AF7:AF16" si="0">COUNTIF(B7:AE7,"غ")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG7" s="36">
         <f t="shared" ref="AG7:AG16" si="1">SUMIF(B7:AE7,"&gt;"&amp;0)+SUMIF(B7:AE7,"&lt;"&amp;0)</f>
@@ -4129,15 +4131,15 @@
       </c>
       <c r="AI7" s="38">
         <f>IF('بيانات الموظفين'!C5="","-",30-AF7)</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ7" s="6">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND(('بيانات الموظفين'!C5/30)*AF7,2))</f>
-        <v>700000</v>
+        <v>933333.33</v>
       </c>
       <c r="AK7" s="39">
         <f>IF('بيانات الموظفين'!C5="","-",ROUND('بيانات الموظفين'!C5+IF(ISNUMBER(AH7),AH7,0)-IF(ISNUMBER(AJ7),AJ7,0),2))</f>
-        <v>6300000</v>
+        <v>6066666.6699999999</v>
       </c>
     </row>
     <row r="8" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4764,7 +4766,7 @@
       </c>
       <c r="U17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="41">
         <f t="shared" si="2"/>
@@ -4808,7 +4810,7 @@
       </c>
       <c r="AF17" s="41">
         <f>SUM(AF7:AF16)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG17" s="42">
         <f>SUM(AG7:AG16)</f>
@@ -4821,11 +4823,11 @@
       <c r="AI17" s="44"/>
       <c r="AJ17" s="43">
         <f>SUM(AJ7:AJ16)</f>
-        <v>700000</v>
+        <v>933333.33</v>
       </c>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>14600000</v>
+        <v>14366666.67</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4910,11 +4912,11 @@
       </c>
       <c r="D21" s="45">
         <f t="shared" ref="D21:D30" si="3">AF7</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" ref="E21:E30" si="4">AJ7</f>
-        <v>700000</v>
+        <v>933333.33</v>
       </c>
       <c r="F21" s="46">
         <f t="shared" ref="F21:F30" si="5">AG7</f>
@@ -4926,7 +4928,7 @@
       </c>
       <c r="H21" s="39">
         <f t="shared" ref="H21:H30" si="7">AK7</f>
-        <v>6300000</v>
+        <v>6066666.6699999999</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5237,11 +5239,11 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="8"/>
-        <v>700000</v>
+        <v>933333.33</v>
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
@@ -5253,7 +5255,7 @@
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>14600000</v>
+        <v>14366666.67</v>
       </c>
     </row>
   </sheetData>

--- a/ضبط_رواتب_الموظفين.xlsx
+++ b/ضبط_رواتب_الموظفين.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60331D28-03CF-4FA6-A413-116692F874EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D45C101-73B9-411B-A40A-FFA0AE6E4F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الملخص السنوي" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="120">
   <si>
     <t>الملخص السنوي الشامل — 2026</t>
   </si>
@@ -1483,11 +1483,11 @@
       </c>
       <c r="I6" s="10">
         <f>IF(ISNUMBER(يونيو!AK8),يونيو!AK8,"")</f>
-        <v>2843750</v>
+        <v>2838888.89</v>
       </c>
       <c r="J6" s="10">
         <f>IF(ISNUMBER(يوليو!AL8),يوليو!AL8,"")</f>
-        <v>2688709.68</v>
+        <v>2702150.54</v>
       </c>
       <c r="K6" s="10">
         <f>IF(ISNUMBER(أغسطس!AL8),أغسطس!AL8,"")</f>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="L6" s="10">
         <f>IF(ISNUMBER(سبتمبر!AK8),سبتمبر!AK8,"")</f>
-        <v>3000000</v>
+        <v>2625000</v>
       </c>
       <c r="M6" s="10">
         <f>IF(ISNUMBER(أكتوبر!AL8),أكتوبر!AL8,"")</f>
@@ -1511,11 +1511,11 @@
       </c>
       <c r="P6" s="6">
         <f>IF(ISNUMBER(يناير!AK8),يناير!AK8,0)+IF(ISNUMBER(فبراير!AH8),فبراير!AH8,0)+IF(ISNUMBER(مارس!AK8),مارس!AK8,0)+IF(ISNUMBER(أبريل!AJ8),أبريل!AJ8,0)+IF(ISNUMBER(مايو!AK8),مايو!AK8,0)+IF(ISNUMBER(يونيو!AJ8),يونيو!AJ8,0)+IF(ISNUMBER(يوليو!AK8),يوليو!AK8,0)+IF(ISNUMBER(أغسطس!AK8),أغسطس!AK8,0)+IF(ISNUMBER(سبتمبر!AJ8),سبتمبر!AJ8,0)+IF(ISNUMBER(أكتوبر!AK8),أكتوبر!AK8,0)+IF(ISNUMBER(نوفمبر!AJ8),نوفمبر!AJ8,0)+IF(ISNUMBER(ديسمبر!AK8),ديسمبر!AK8,0)</f>
-        <v>490322.58</v>
+        <v>890322.58000000007</v>
       </c>
       <c r="Q6" s="7">
         <f t="shared" si="0"/>
-        <v>36132459.68</v>
+        <v>35766039.43</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1552,11 +1552,11 @@
       </c>
       <c r="I7" s="5">
         <f>IF(ISNUMBER(يونيو!AK9),يونيو!AK9,"")</f>
-        <v>2296875</v>
+        <v>2300925.92</v>
       </c>
       <c r="J7" s="5">
         <f>IF(ISNUMBER(يوليو!AL9),يوليو!AL9,"")</f>
-        <v>2351478.4900000002</v>
+        <v>2368279.5699999998</v>
       </c>
       <c r="K7" s="5">
         <f>IF(ISNUMBER(أغسطس!AL9),أغسطس!AL9,"")</f>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L7" s="5">
         <f>IF(ISNUMBER(سبتمبر!AK9),سبتمبر!AK9,"")</f>
-        <v>2500000</v>
+        <v>2365740.7400000002</v>
       </c>
       <c r="M7" s="5">
         <f>IF(ISNUMBER(أكتوبر!AL9),أكتوبر!AL9,"")</f>
@@ -1580,11 +1580,11 @@
       </c>
       <c r="P7" s="6">
         <f>IF(ISNUMBER(يناير!AK9),يناير!AK9,0)+IF(ISNUMBER(فبراير!AH9),فبراير!AH9,0)+IF(ISNUMBER(مارس!AK9),مارس!AK9,0)+IF(ISNUMBER(أبريل!AJ9),أبريل!AJ9,0)+IF(ISNUMBER(مايو!AK9),مايو!AK9,0)+IF(ISNUMBER(يونيو!AJ9),يونيو!AJ9,0)+IF(ISNUMBER(يوليو!AK9),يوليو!AK9,0)+IF(ISNUMBER(أغسطس!AK9),أغسطس!AK9,0)+IF(ISNUMBER(سبتمبر!AJ9),سبتمبر!AJ9,0)+IF(ISNUMBER(أكتوبر!AK9),أكتوبر!AK9,0)+IF(ISNUMBER(نوفمبر!AJ9),نوفمبر!AJ9,0)+IF(ISNUMBER(ديسمبر!AK9),ديسمبر!AK9,0)</f>
-        <v>2747311.83</v>
+        <v>2913978.5</v>
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="0"/>
-        <v>27648353.469999999</v>
+        <v>27534946.209999993</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1621,11 +1621,11 @@
       </c>
       <c r="I8" s="10">
         <f>IF(ISNUMBER(يونيو!AK10),يونيو!AK10,"")</f>
-        <v>471666.67</v>
+        <v>472592.59</v>
       </c>
       <c r="J8" s="10">
         <f>IF(ISNUMBER(يوليو!AL10),يوليو!AL10,"")</f>
-        <v>658924.73</v>
+        <v>666093.18999999994</v>
       </c>
       <c r="K8" s="10">
         <f>IF(ISNUMBER(أغسطس!AL10),أغسطس!AL10,"")</f>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Q8" s="7">
         <f t="shared" si="0"/>
-        <v>9290591.4199999999</v>
+        <v>9298685.7999999989</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1690,11 +1690,11 @@
       </c>
       <c r="I9" s="5">
         <f>IF(ISNUMBER(يونيو!AK11),يونيو!AK11,"")</f>
-        <v>504166.66</v>
+        <v>507407.4</v>
       </c>
       <c r="J9" s="5">
         <f>IF(ISNUMBER(يوليو!AL11),يوليو!AL11,"")</f>
-        <v>1619086.02</v>
+        <v>1632974.91</v>
       </c>
       <c r="K9" s="5">
         <f>IF(ISNUMBER(أغسطس!AL11),أغسطس!AL11,"")</f>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Q9" s="7">
         <f t="shared" si="0"/>
-        <v>22394220.439999998</v>
+        <v>22411350.07</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -2101,11 +2101,11 @@
       </c>
       <c r="I15" s="11">
         <f t="shared" si="1"/>
-        <v>12416458.33</v>
+        <v>12419814.800000001</v>
       </c>
       <c r="J15" s="11">
         <f t="shared" si="1"/>
-        <v>13422499.99</v>
+        <v>13473799.279999999</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="1"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="L15" s="11">
         <f t="shared" si="1"/>
-        <v>14366666.67</v>
+        <v>13857407.41</v>
       </c>
       <c r="M15" s="11">
         <f t="shared" si="1"/>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="P15" s="12">
         <f t="shared" si="1"/>
-        <v>10599569.91</v>
+        <v>11166236.580000002</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="1"/>
-        <v>176078528.20999998</v>
+        <v>175623924.70999998</v>
       </c>
     </row>
   </sheetData>
@@ -4147,61 +4147,99 @@
         <f>'بيانات الموظفين'!B6</f>
         <v>هيثم صمادي</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
+      <c r="B8" s="40">
+        <v>1</v>
+      </c>
+      <c r="C8" s="40">
+        <v>-1.75</v>
+      </c>
+      <c r="D8" s="40">
+        <v>2</v>
+      </c>
       <c r="E8" s="34"/>
       <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="K8" s="40"/>
+      <c r="G8" s="40">
+        <v>1</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="40">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="40">
+        <v>3</v>
+      </c>
+      <c r="K8" s="40">
+        <v>-4</v>
+      </c>
       <c r="L8" s="34"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
+      <c r="M8" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="O8" s="40">
+        <v>-2</v>
+      </c>
+      <c r="P8" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="Q8" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="R8" s="40">
+        <v>-1.5</v>
+      </c>
       <c r="S8" s="34"/>
-      <c r="T8" s="40"/>
+      <c r="T8" s="40">
+        <v>0.5</v>
+      </c>
       <c r="U8" s="40"/>
-      <c r="V8" s="40"/>
+      <c r="V8" s="40">
+        <v>1.5</v>
+      </c>
       <c r="W8" s="40"/>
       <c r="X8" s="40"/>
-      <c r="Y8" s="40"/>
+      <c r="Y8" s="40">
+        <v>-0.5</v>
+      </c>
       <c r="Z8" s="34"/>
-      <c r="AA8" s="40"/>
-      <c r="AB8" s="40"/>
-      <c r="AC8" s="40"/>
+      <c r="AA8" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB8" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC8" s="40" t="s">
+        <v>39</v>
+      </c>
       <c r="AD8" s="40"/>
       <c r="AE8" s="40"/>
       <c r="AF8" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG8" s="36">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH8" s="37" t="str">
+        <v>2.25</v>
+      </c>
+      <c r="AH8" s="37">
         <f>IF(OR('بيانات الموظفين'!C6="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AG8=0),"-",ROUND(AG8*(('بيانات الموظفين'!C6/30)/'بيانات الموظفين'!G2),2))</f>
-        <v>-</v>
+        <v>25000</v>
       </c>
       <c r="AI8" s="38">
         <f>IF('بيانات الموظفين'!C6="","-",30-AF8)</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AJ8" s="6">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND(('بيانات الموظفين'!C6/30)*AF8,2))</f>
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="AK8" s="39">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND('بيانات الموظفين'!C6+IF(ISNUMBER(AH8),AH8,0)-IF(ISNUMBER(AJ8),AJ8,0),2))</f>
-        <v>3000000</v>
+        <v>2625000</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4209,59 +4247,95 @@
         <f>'بيانات الموظفين'!B7</f>
         <v>حسام كبريتة</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
+      <c r="B9" s="33">
+        <v>1</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="33">
+        <v>1.5</v>
+      </c>
       <c r="E9" s="34"/>
       <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
+      <c r="G9" s="33">
+        <v>1</v>
+      </c>
       <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
+      <c r="I9" s="33">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="33">
+        <v>3</v>
+      </c>
+      <c r="K9" s="33">
+        <v>-4</v>
+      </c>
       <c r="L9" s="34"/>
       <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
+      <c r="N9" s="33">
+        <v>2.5</v>
+      </c>
+      <c r="O9" s="33">
+        <v>-2</v>
+      </c>
+      <c r="P9" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="Q9" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="R9" s="33">
+        <v>-1.5</v>
+      </c>
       <c r="S9" s="34"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
-      <c r="V9" s="33"/>
+      <c r="T9" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="U9" s="33">
+        <v>-0.5</v>
+      </c>
+      <c r="V9" s="33">
+        <v>1.5</v>
+      </c>
       <c r="W9" s="33"/>
       <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
+      <c r="Y9" s="33">
+        <v>-0.5</v>
+      </c>
       <c r="Z9" s="34"/>
-      <c r="AA9" s="33"/>
+      <c r="AA9" s="33">
+        <v>2.5</v>
+      </c>
       <c r="AB9" s="33"/>
       <c r="AC9" s="33"/>
-      <c r="AD9" s="33"/>
+      <c r="AD9" s="33">
+        <v>-1</v>
+      </c>
       <c r="AE9" s="33"/>
       <c r="AF9" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9" s="36">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH9" s="37" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="AH9" s="37">
         <f>IF(OR('بيانات الموظفين'!C7="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AG9=0),"-",ROUND(AG9*(('بيانات الموظفين'!C7/30)/'بيانات الموظفين'!G2),2))</f>
-        <v>-</v>
+        <v>32407.41</v>
       </c>
       <c r="AI9" s="38">
         <f>IF('بيانات الموظفين'!C7="","-",30-AF9)</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ9" s="6">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND(('بيانات الموظفين'!C7/30)*AF9,2))</f>
-        <v>0</v>
+        <v>166666.67000000001</v>
       </c>
       <c r="AK9" s="39">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND('بيانات الموظفين'!C7+IF(ISNUMBER(AH9),AH9,0)-IF(ISNUMBER(AJ9),AJ9,0),2))</f>
-        <v>2500000</v>
+        <v>2365740.7400000002</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4694,7 +4768,7 @@
       </c>
       <c r="C17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="41">
         <f t="shared" si="2"/>
@@ -4734,7 +4808,7 @@
       </c>
       <c r="M17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="41">
         <f t="shared" si="2"/>
@@ -4762,7 +4836,7 @@
       </c>
       <c r="T17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" s="41">
         <f t="shared" si="2"/>
@@ -4790,15 +4864,15 @@
       </c>
       <c r="AA17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" s="41">
         <f t="shared" si="2"/>
@@ -4810,24 +4884,24 @@
       </c>
       <c r="AF17" s="41">
         <f>SUM(AF7:AF16)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AG17" s="42">
         <f>SUM(AG7:AG16)</f>
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH17" s="43">
         <f>SUM(AH7:AH16)</f>
-        <v>0</v>
+        <v>57407.41</v>
       </c>
       <c r="AI17" s="44"/>
       <c r="AJ17" s="43">
         <f>SUM(AJ7:AJ16)</f>
-        <v>933333.33</v>
+        <v>1500000</v>
       </c>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>14366666.67</v>
+        <v>13857407.41</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4945,23 +5019,23 @@
       </c>
       <c r="D22" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="F22" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="37" t="str">
+        <v>2.25</v>
+      </c>
+      <c r="G22" s="37">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>25000</v>
       </c>
       <c r="H22" s="39">
         <f t="shared" si="7"/>
-        <v>3000000</v>
+        <v>2625000</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -4978,23 +5052,23 @@
       </c>
       <c r="D23" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>166666.67000000001</v>
       </c>
       <c r="F23" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="37" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="G23" s="37">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>32407.41</v>
       </c>
       <c r="H23" s="39">
         <f t="shared" si="7"/>
-        <v>2500000</v>
+        <v>2365740.7400000002</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5239,23 +5313,23 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="8"/>
-        <v>933333.33</v>
+        <v>1500000</v>
       </c>
       <c r="F31" s="47">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>57407.41</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>14366666.67</v>
+        <v>13857407.41</v>
       </c>
     </row>
   </sheetData>
@@ -10079,7 +10153,7 @@
       <c r="E2" s="63"/>
       <c r="F2" s="63"/>
       <c r="G2" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>24</v>
@@ -18313,7 +18387,7 @@
       </c>
       <c r="AH8" s="37">
         <f>IF(OR('بيانات الموظفين'!C6="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AG8=0),"-",ROUND(AG8*(('بيانات الموظفين'!C6/30)/'بيانات الموظفين'!G2),2))</f>
-        <v>43750</v>
+        <v>38888.89</v>
       </c>
       <c r="AI8" s="38">
         <f>IF('بيانات الموظفين'!C6="","-",30-AF8)</f>
@@ -18325,7 +18399,7 @@
       </c>
       <c r="AK8" s="39">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND('بيانات الموظفين'!C6+IF(ISNUMBER(AH8),AH8,0)-IF(ISNUMBER(AJ8),AJ8,0),2))</f>
-        <v>2843750</v>
+        <v>2838888.89</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -18387,7 +18461,7 @@
       </c>
       <c r="AH9" s="37">
         <f>IF(OR('بيانات الموظفين'!C7="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AG9=0),"-",ROUND(AG9*(('بيانات الموظفين'!C7/30)/'بيانات الموظفين'!G2),2))</f>
-        <v>-36458.33</v>
+        <v>-32407.41</v>
       </c>
       <c r="AI9" s="38">
         <f>IF('بيانات الموظفين'!C7="","-",30-AF9)</f>
@@ -18399,7 +18473,7 @@
       </c>
       <c r="AK9" s="39">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND('بيانات الموظفين'!C7+IF(ISNUMBER(AH9),AH9,0)-IF(ISNUMBER(AJ9),AJ9,0),2))</f>
-        <v>2296875</v>
+        <v>2300925.92</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -18473,7 +18547,7 @@
       </c>
       <c r="AH10" s="37">
         <f>IF(OR('بيانات الموظفين'!C8="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AG10=0),"-",ROUND(AG10*(('بيانات الموظفين'!C8/30)/'بيانات الموظفين'!G2),2))</f>
-        <v>-8333.33</v>
+        <v>-7407.41</v>
       </c>
       <c r="AI10" s="38">
         <f>IF('بيانات الموظفين'!C8="","-",30-AF10)</f>
@@ -18485,7 +18559,7 @@
       </c>
       <c r="AK10" s="39">
         <f>IF('بيانات الموظفين'!C8="","-",ROUND('بيانات الموظفين'!C8+IF(ISNUMBER(AH10),AH10,0)-IF(ISNUMBER(AJ10),AJ10,0),2))</f>
-        <v>471666.67</v>
+        <v>472592.59</v>
       </c>
     </row>
     <row r="11" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -18583,7 +18657,7 @@
       </c>
       <c r="AH11" s="37">
         <f>IF(OR('بيانات الموظفين'!C9="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AG11=0),"-",ROUND(AG11*(('بيانات الموظفين'!C9/30)/'بيانات الموظفين'!G2),2))</f>
-        <v>-29166.67</v>
+        <v>-25925.93</v>
       </c>
       <c r="AI11" s="38">
         <f>IF('بيانات الموظفين'!C9="","-",30-AF11)</f>
@@ -18595,7 +18669,7 @@
       </c>
       <c r="AK11" s="39">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND('بيانات الموظفين'!C9+IF(ISNUMBER(AH11),AH11,0)-IF(ISNUMBER(AJ11),AJ11,0),2))</f>
-        <v>504166.66</v>
+        <v>507407.4</v>
       </c>
     </row>
     <row r="12" spans="1:37" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -19032,7 +19106,7 @@
       </c>
       <c r="AH17" s="43">
         <f>SUM(AH7:AH16)</f>
-        <v>-30208.33</v>
+        <v>-26851.86</v>
       </c>
       <c r="AI17" s="44"/>
       <c r="AJ17" s="43">
@@ -19041,7 +19115,7 @@
       </c>
       <c r="AK17" s="43">
         <f>SUM(AK7:AK16)</f>
-        <v>12416458.33</v>
+        <v>12419814.800000001</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19171,11 +19245,11 @@
       </c>
       <c r="G22" s="37">
         <f t="shared" si="6"/>
-        <v>43750</v>
+        <v>38888.89</v>
       </c>
       <c r="H22" s="39">
         <f t="shared" si="7"/>
-        <v>2843750</v>
+        <v>2838888.89</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19204,11 +19278,11 @@
       </c>
       <c r="G23" s="37">
         <f t="shared" si="6"/>
-        <v>-36458.33</v>
+        <v>-32407.41</v>
       </c>
       <c r="H23" s="39">
         <f t="shared" si="7"/>
-        <v>2296875</v>
+        <v>2300925.92</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19237,11 +19311,11 @@
       </c>
       <c r="G24" s="37">
         <f t="shared" si="6"/>
-        <v>-8333.33</v>
+        <v>-7407.41</v>
       </c>
       <c r="H24" s="39">
         <f t="shared" si="7"/>
-        <v>471666.67</v>
+        <v>472592.59</v>
       </c>
     </row>
     <row r="25" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19270,11 +19344,11 @@
       </c>
       <c r="G25" s="37">
         <f t="shared" si="6"/>
-        <v>-29166.67</v>
+        <v>-25925.93</v>
       </c>
       <c r="H25" s="39">
         <f t="shared" si="7"/>
-        <v>504166.66</v>
+        <v>507407.4</v>
       </c>
     </row>
     <row r="26" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19465,11 +19539,11 @@
       </c>
       <c r="G31" s="12">
         <f t="shared" si="8"/>
-        <v>-30208.33</v>
+        <v>-26851.86</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>12416458.33</v>
+        <v>12419814.800000001</v>
       </c>
     </row>
   </sheetData>
@@ -19960,7 +20034,7 @@
       </c>
       <c r="AI8" s="37">
         <f>IF(OR('بيانات الموظفين'!C6="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH8=0),"-",ROUND(AH8*(('بيانات الموظفين'!C6/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-120967.74</v>
+        <v>-107526.88</v>
       </c>
       <c r="AJ8" s="38">
         <f>IF('بيانات الموظفين'!C6="","-",31-AG8)</f>
@@ -19972,7 +20046,7 @@
       </c>
       <c r="AL8" s="39">
         <f>IF('بيانات الموظفين'!C6="","-",ROUND('بيانات الموظفين'!C6+ROUND('بيانات الموظفين'!C6/30,2)+IF(ISNUMBER(AI8),AI8,0)-IF(ISNUMBER(AK8),AK8,0),2))</f>
-        <v>2688709.68</v>
+        <v>2702150.54</v>
       </c>
     </row>
     <row r="9" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20049,7 +20123,7 @@
       </c>
       <c r="AI9" s="37">
         <f>IF(OR('بيانات الموظفين'!C7="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH9=0),"-",ROUND(AH9*(('بيانات الموظفين'!C7/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-151209.68</v>
+        <v>-134408.6</v>
       </c>
       <c r="AJ9" s="38">
         <f>IF('بيانات الموظفين'!C7="","-",31-AG9)</f>
@@ -20061,7 +20135,7 @@
       </c>
       <c r="AL9" s="39">
         <f>IF('بيانات الموظفين'!C7="","-",ROUND('بيانات الموظفين'!C7+ROUND('بيانات الموظفين'!C7/30,2)+IF(ISNUMBER(AI9),AI9,0)-IF(ISNUMBER(AK9),AK9,0),2))</f>
-        <v>2351478.4900000002</v>
+        <v>2368279.5699999998</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20132,7 +20206,7 @@
       </c>
       <c r="AI10" s="37">
         <f>IF(OR('بيانات الموظفين'!C8="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH10=0),"-",ROUND(AH10*(('بيانات الموظفين'!C8/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-64516.13</v>
+        <v>-57347.67</v>
       </c>
       <c r="AJ10" s="38">
         <f>IF('بيانات الموظفين'!C8="","-",31-AG10)</f>
@@ -20144,7 +20218,7 @@
       </c>
       <c r="AL10" s="39">
         <f>IF('بيانات الموظفين'!C8="","-",ROUND('بيانات الموظفين'!C8+ROUND('بيانات الموظفين'!C8/30,2)+IF(ISNUMBER(AI10),AI10,0)-IF(ISNUMBER(AK10),AK10,0),2))</f>
-        <v>658924.73</v>
+        <v>666093.18999999994</v>
       </c>
     </row>
     <row r="11" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20217,7 +20291,7 @@
       </c>
       <c r="AI11" s="37">
         <f>IF(OR('بيانات الموظفين'!C9="",NOT(ISNUMBER('بيانات الموظفين'!G2)),AH11=0),"-",ROUND(AH11*(('بيانات الموظفين'!C9/31)/'بيانات الموظفين'!G2),2))</f>
-        <v>-125000</v>
+        <v>-111111.11</v>
       </c>
       <c r="AJ11" s="38">
         <f>IF('بيانات الموظفين'!C9="","-",31-AG11)</f>
@@ -20229,7 +20303,7 @@
       </c>
       <c r="AL11" s="39">
         <f>IF('بيانات الموظفين'!C9="","-",ROUND('بيانات الموظفين'!C9+ROUND('بيانات الموظفين'!C9/30,2)+IF(ISNUMBER(AI11),AI11,0)-IF(ISNUMBER(AK11),AK11,0),2))</f>
-        <v>1619086.02</v>
+        <v>1632974.91</v>
       </c>
     </row>
     <row r="12" spans="1:38" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20675,7 +20749,7 @@
       </c>
       <c r="AI17" s="43">
         <f>SUM(AI7:AI16)</f>
-        <v>-461693.55</v>
+        <v>-410394.26</v>
       </c>
       <c r="AJ17" s="44"/>
       <c r="AK17" s="43">
@@ -20684,7 +20758,7 @@
       </c>
       <c r="AL17" s="43">
         <f>SUM(AL7:AL16)</f>
-        <v>13422499.99</v>
+        <v>13473799.279999999</v>
       </c>
     </row>
     <row r="18" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -20815,11 +20889,11 @@
       </c>
       <c r="G22" s="37">
         <f t="shared" si="6"/>
-        <v>-120967.74</v>
+        <v>-107526.88</v>
       </c>
       <c r="H22" s="39">
         <f t="shared" si="7"/>
-        <v>2688709.68</v>
+        <v>2702150.54</v>
       </c>
     </row>
     <row r="23" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20848,11 +20922,11 @@
       </c>
       <c r="G23" s="37">
         <f t="shared" si="6"/>
-        <v>-151209.68</v>
+        <v>-134408.6</v>
       </c>
       <c r="H23" s="39">
         <f t="shared" si="7"/>
-        <v>2351478.4900000002</v>
+        <v>2368279.5699999998</v>
       </c>
     </row>
     <row r="24" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20881,11 +20955,11 @@
       </c>
       <c r="G24" s="37">
         <f t="shared" si="6"/>
-        <v>-64516.13</v>
+        <v>-57347.67</v>
       </c>
       <c r="H24" s="39">
         <f t="shared" si="7"/>
-        <v>658924.73</v>
+        <v>666093.18999999994</v>
       </c>
     </row>
     <row r="25" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20914,11 +20988,11 @@
       </c>
       <c r="G25" s="37">
         <f t="shared" si="6"/>
-        <v>-125000</v>
+        <v>-111111.11</v>
       </c>
       <c r="H25" s="39">
         <f t="shared" si="7"/>
-        <v>1619086.02</v>
+        <v>1632974.91</v>
       </c>
     </row>
     <row r="26" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21109,11 +21183,11 @@
       </c>
       <c r="G31" s="12">
         <f t="shared" si="8"/>
-        <v>-461693.55</v>
+        <v>-410394.26</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="8"/>
-        <v>13422499.99</v>
+        <v>13473799.279999999</v>
       </c>
     </row>
   </sheetData>
